--- a/static/files/targets.xlsx
+++ b/static/files/targets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32943C70-2127-4FE7-9F85-67670AF5BE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E44023-3309-4F45-B9CB-69C1C4D18C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB0B02AC-0218-406F-81FB-4EC7842BB88E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Approval Manager</t>
   </si>
@@ -45,13 +45,10 @@
     <t>Lead</t>
   </si>
   <si>
-    <t>Udaya</t>
-  </si>
-  <si>
     <t>Web Development</t>
   </si>
   <si>
-    <t>main</t>
+    <t>Approval manager</t>
   </si>
 </sst>
 </file>
@@ -480,13 +477,13 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/static/files/targets.xlsx
+++ b/static/files/targets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E44023-3309-4F45-B9CB-69C1C4D18C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC463BE0-E76E-46F7-B00A-EF673C47E99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB0B02AC-0218-406F-81FB-4EC7842BB88E}"/>
   </bookViews>
@@ -618,8 +618,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{95B73239-FE10-4ABD-879A-8A13BFC4C717}">
-      <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{ED386E54-A498-4BA5-8750-8685AB51F53A}">
+      <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training,Heymax,Trademo,ONECLICKLCA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
